--- a/data/trans_orig/DCD_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129935</t>
+          <t>130784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166436</t>
+          <t>166054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>337774</t>
+          <t>338406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>380839</t>
+          <t>381466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>478853</t>
+          <t>478189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>535781</t>
+          <t>533562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348502</t>
+          <t>348884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385003</t>
+          <t>384154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374669</t>
+          <t>374042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417734</t>
+          <t>417102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>734665</t>
+          <t>736884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>791593</t>
+          <t>792257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>186435</t>
+          <t>178842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306627</t>
+          <t>300416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>328526</t>
+          <t>343442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>518303</t>
+          <t>520280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>561287</t>
+          <t>570704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>800648</t>
+          <t>802515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1983700</t>
+          <t>1989911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2103892</t>
+          <t>2111485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1719520</t>
+          <t>1717543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1909297</t>
+          <t>1894381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3727502</t>
+          <t>3725635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3966863</t>
+          <t>3957446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>41952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69208</t>
+          <t>68137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115474</t>
+          <t>116010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152161</t>
+          <t>152992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166714</t>
+          <t>167349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211607</t>
+          <t>213624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577415</t>
+          <t>578486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>604523</t>
+          <t>604671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>508302</t>
+          <t>507471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544989</t>
+          <t>544453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1095479</t>
+          <t>1093462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1140372</t>
+          <t>1139737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>366010</t>
+          <t>366213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>517940</t>
+          <t>515891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>755886</t>
+          <t>767509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1027227</t>
+          <t>1031369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1235251</t>
+          <t>1227786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1519430</t>
+          <t>1517951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2933949</t>
+          <t>2935998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3085879</t>
+          <t>3085676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2626567</t>
+          <t>2622425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2897908</t>
+          <t>2886285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5586253</t>
+          <t>5587732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5870432</t>
+          <t>5877897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>147842</t>
+          <t>158391</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>137777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166054</t>
+          <t>178088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>359163</t>
+          <t>386033</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>338406</t>
+          <t>364732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>381466</t>
+          <t>407236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>507006</t>
+          <t>544423</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>478189</t>
+          <t>513982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>533562</t>
+          <t>576379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>367096</t>
+          <t>420138</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348884</t>
+          <t>400441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384154</t>
+          <t>440752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>396345</t>
+          <t>436005</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374042</t>
+          <t>414802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417102</t>
+          <t>457306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>763440</t>
+          <t>856144</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>736884</t>
+          <t>824188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>792257</t>
+          <t>886585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>259870</t>
+          <t>277829</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178842</t>
+          <t>248206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>300416</t>
+          <t>312129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>454141</t>
+          <t>508478</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>343442</t>
+          <t>474293</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>520280</t>
+          <t>548126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>714010</t>
+          <t>786307</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>570704</t>
+          <t>740555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>802515</t>
+          <t>842750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2030457</t>
+          <t>1952737</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1989911</t>
+          <t>1918437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2111485</t>
+          <t>1982360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1783682</t>
+          <t>1662914</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1717543</t>
+          <t>1623266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1894381</t>
+          <t>1697099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3814140</t>
+          <t>3615652</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3725635</t>
+          <t>3559209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3957446</t>
+          <t>3661404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54868</t>
+          <t>60118</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41952</t>
+          <t>46087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68137</t>
+          <t>75100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>134263</t>
+          <t>153639</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116010</t>
+          <t>135076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152992</t>
+          <t>175375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>189130</t>
+          <t>213758</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167349</t>
+          <t>188792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213624</t>
+          <t>241525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>591755</t>
+          <t>651469</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>578486</t>
+          <t>636487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>604671</t>
+          <t>665500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>526200</t>
+          <t>581238</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>507471</t>
+          <t>559502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544453</t>
+          <t>599801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1117956</t>
+          <t>1232706</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1093462</t>
+          <t>1204939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1139737</t>
+          <t>1257672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>366213</t>
+          <t>454333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>515891</t>
+          <t>538621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>947567</t>
+          <t>1048151</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>767509</t>
+          <t>1002854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1031369</t>
+          <t>1095352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1410147</t>
+          <t>1544489</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1227786</t>
+          <t>1483039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1517951</t>
+          <t>1605829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2989309</t>
+          <t>3024345</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2935998</t>
+          <t>2982062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3085676</t>
+          <t>3066350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2706227</t>
+          <t>2680156</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2622425</t>
+          <t>2632955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2886285</t>
+          <t>2725453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5695536</t>
+          <t>5704501</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5587732</t>
+          <t>5643161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5877897</t>
+          <t>5765951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>79,54%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
